--- a/samples/models/monte-carlo.xlsx
+++ b/samples/models/monte-carlo.xlsx
@@ -1,63 +1,393 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Model" sheetId="1" r:id="rId1"/>
-    <sheet name="Source data" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Cover" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Historicals" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="MonteCarlo" state="visible" r:id="rId6"/>
   </sheets>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
+  <si>
+    <t>Financial Model: Aurora Retail Co.</t>
+  </si>
+  <si>
+    <t>Prepared with Finance Studio on 10/29/2026</t>
+  </si>
+  <si>
+    <t>Blue = input you can change · Green = linked to Historicals · Black = formula</t>
+  </si>
+  <si>
+    <t>Source data</t>
+  </si>
+  <si>
+    <t>Aurora Retail Co. · 2020–2024 (5 periods)</t>
+  </si>
+  <si>
+    <t>Contents</t>
+  </si>
+  <si>
+    <t>Sheet</t>
+  </si>
+  <si>
+    <t>What it contains</t>
+  </si>
+  <si>
+    <t>Historicals</t>
+  </si>
+  <si>
+    <t>Your uploaded financial statements (the source for linked figures)</t>
+  </si>
+  <si>
+    <t>MonteCarlo</t>
+  </si>
+  <si>
+    <t>Monte Carlo valuation range (simulation results)</t>
+  </si>
+  <si>
+    <t>How to use this model</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Blue cells are inputs. Change them and every formula updates.</t>
+  </si>
+  <si>
+    <t>Linked</t>
+  </si>
+  <si>
+    <t>Green cells link to the Historicals sheet.</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>Black cells are formulas. Avoid typing over them.</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t>Shaded cells are key outputs.</t>
+  </si>
+  <si>
+    <t>Models are planning tools based on the data and assumptions provided. They are not investment advice.</t>
+  </si>
+  <si>
+    <t>Historical Financial Statements</t>
+  </si>
+  <si>
+    <t>Aurora Retail Co. · as uploaded</t>
+  </si>
+  <si>
+    <t>Financial statements</t>
+  </si>
+  <si>
+    <t>Line item</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Cost of Goods Sold</t>
+  </si>
+  <si>
+    <t>Gross Profit</t>
+  </si>
+  <si>
+    <t>Operating Expenses</t>
+  </si>
+  <si>
+    <t>EBITDA</t>
+  </si>
+  <si>
+    <t>D&amp;A</t>
+  </si>
+  <si>
+    <t>EBIT</t>
+  </si>
+  <si>
+    <t>Interest Expense</t>
+  </si>
+  <si>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>Current Assets</t>
+  </si>
+  <si>
+    <t>Total Assets</t>
+  </si>
+  <si>
+    <t>Current Liabilities</t>
+  </si>
+  <si>
+    <t>Total Liabilities</t>
+  </si>
+  <si>
+    <t>Total Debt</t>
+  </si>
+  <si>
+    <t>Equity</t>
+  </si>
+  <si>
+    <t>CapEx</t>
+  </si>
+  <si>
+    <t>Operating Cash Flow</t>
+  </si>
+  <si>
+    <t>Monte Carlo Valuation</t>
+  </si>
+  <si>
+    <t>Aurora Retail Co. · simulated DCF outcomes</t>
+  </si>
+  <si>
+    <t>Assumptions used in the simulation</t>
+  </si>
+  <si>
+    <t>Base revenue</t>
+  </si>
+  <si>
+    <t>Growth mean</t>
+  </si>
+  <si>
+    <t>Growth std. dev.</t>
+  </si>
+  <si>
+    <t>EBITDA margin mean</t>
+  </si>
+  <si>
+    <t>Margin std. dev.</t>
+  </si>
+  <si>
+    <t>WACC</t>
+  </si>
+  <si>
+    <t>Terminal growth</t>
+  </si>
+  <si>
+    <t>Net debt</t>
+  </si>
+  <si>
+    <t>Simulations</t>
+  </si>
+  <si>
+    <t>Results below were simulated in Finance Studio. Change the assumptions in the app and export again to re-run.</t>
+  </si>
+  <si>
+    <t>Results: enterprise value</t>
+  </si>
+  <si>
+    <t>P10 (downside)</t>
+  </si>
+  <si>
+    <t>P50 (median)</t>
+  </si>
+  <si>
+    <t>P90 (upside)</t>
+  </si>
+  <si>
+    <t>Base case (no randomness)</t>
+  </si>
+  <si>
+    <t>Probability above base case</t>
+  </si>
+  <si>
+    <t>Distribution</t>
+  </si>
+  <si>
+    <t>Bucket</t>
+  </si>
+  <si>
+    <t>From</t>
+  </si>
+  <si>
+    <t>To</t>
+  </si>
+  <si>
+    <t>Bucket 1</t>
+  </si>
+  <si>
+    <t>Bucket 2</t>
+  </si>
+  <si>
+    <t>Bucket 3</t>
+  </si>
+  <si>
+    <t>Bucket 4</t>
+  </si>
+  <si>
+    <t>Bucket 5</t>
+  </si>
+  <si>
+    <t>Bucket 6</t>
+  </si>
+  <si>
+    <t>Bucket 7</t>
+  </si>
+  <si>
+    <t>Bucket 8</t>
+  </si>
+  <si>
+    <t>Bucket 9</t>
+  </si>
+  <si>
+    <t>Bucket 10</t>
+  </si>
+  <si>
+    <t>Bucket 11</t>
+  </si>
+  <si>
+    <t>Bucket 12</t>
+  </si>
+  <si>
+    <t>Bucket 13</t>
+  </si>
+  <si>
+    <t>Bucket 14</t>
+  </si>
+  <si>
+    <t>Bucket 15</t>
+  </si>
+  <si>
+    <t>Bucket 16</t>
+  </si>
+  <si>
+    <t>Bucket 17</t>
+  </si>
+  <si>
+    <t>Bucket 18</t>
+  </si>
+  <si>
+    <t>Bucket 19</t>
+  </si>
+  <si>
+    <t>Bucket 20</t>
+  </si>
+  <si>
+    <t>Bucket 21</t>
+  </si>
+  <si>
+    <t>Bucket 22</t>
+  </si>
+  <si>
+    <t>Bucket 23</t>
+  </si>
+  <si>
+    <t>Bucket 24</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="60" formatCode="$#,##0;-$#,##0"/>
-    <numFmt numFmtId="61" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="62" formatCode="0.0%"/>
-    <numFmt numFmtId="63" formatCode="0.00&quot;x&quot;"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;–&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0B2545"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF5C6B80"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF7A8699"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="FF14213D"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF14213D"/>
+    </font>
+    <font>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <color rgb="FF00804A"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0B2545"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B2545"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9EDF3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -65,20 +395,66 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF9AA5B5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF0B2545"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B2545"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="62" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -403,566 +779,1071 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF0B2545"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="36.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" customWidth="1"/>
-    <col min="12" max="12" width="16.83203125" customWidth="1"/>
-    <col min="13" max="13" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Monte Carlo</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Aurora Retail Co. (sample)</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Generated 10/29/2026</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Inputs</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Value</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Base revenue ($)</v>
-      </c>
-      <c r="B5">
-        <v>13100000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Growth mean %</v>
-      </c>
-      <c r="B6">
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Growth std. dev. %</v>
-      </c>
-      <c r="B7">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Margin mean %</v>
-      </c>
-      <c r="B8">
-        <v>22.9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Margin std. dev. %</v>
-      </c>
-      <c r="B9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>WACC %</v>
-      </c>
-      <c r="B10">
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Terminal growth %</v>
-      </c>
-      <c r="B11">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Net debt ($)</v>
-      </c>
-      <c r="B12">
-        <v>-100000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Simulations</v>
-      </c>
-      <c r="B13">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Key results</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Value</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Note</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>P10 (downside)</v>
-      </c>
-      <c r="B16" s="1">
-        <v>20919774.23027678</v>
-      </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>P50 (median)</v>
-      </c>
-      <c r="B17" s="1">
-        <v>29298831.557936855</v>
-      </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>P90 (upside)</v>
-      </c>
-      <c r="B18" s="1">
-        <v>38538820.45687782</v>
-      </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Chance above base case</v>
-      </c>
-      <c r="B19" s="2">
-        <v>0.5105</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Base EV $29.15M</v>
+      <c r="B10" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF0B2545"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="6" width="15" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Line item</v>
-      </c>
-      <c r="B1" t="str">
-        <v>2020</v>
-      </c>
-      <c r="C1" t="str">
-        <v>2021</v>
-      </c>
-      <c r="D1" t="str">
-        <v>2022</v>
-      </c>
-      <c r="E1" t="str">
-        <v>2023</v>
-      </c>
-      <c r="F1" t="str">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Revenue</v>
-      </c>
-      <c r="B2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="13">
         <v>8200000</v>
       </c>
-      <c r="C2">
+      <c r="C7" s="13">
         <v>9100000</v>
       </c>
-      <c r="D2">
+      <c r="D7" s="13">
         <v>10400000</v>
       </c>
-      <c r="E2">
+      <c r="E7" s="13">
         <v>11800000</v>
       </c>
-      <c r="F2">
+      <c r="F7" s="13">
         <v>13100000</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Cost of Goods Sold</v>
-      </c>
-      <c r="B3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="13">
         <v>4900000</v>
       </c>
-      <c r="C3">
+      <c r="C8" s="13">
         <v>5400000</v>
       </c>
-      <c r="D3">
+      <c r="D8" s="13">
         <v>6100000</v>
       </c>
-      <c r="E3">
+      <c r="E8" s="13">
         <v>6800000</v>
       </c>
-      <c r="F3">
+      <c r="F8" s="13">
         <v>7500000</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Gross Profit</v>
-      </c>
-      <c r="B4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="13">
         <v>3300000</v>
       </c>
-      <c r="C4">
+      <c r="C9" s="13">
         <v>3700000</v>
       </c>
-      <c r="D4">
+      <c r="D9" s="13">
         <v>4300000</v>
       </c>
-      <c r="E4">
+      <c r="E9" s="13">
         <v>5000000</v>
       </c>
-      <c r="F4">
+      <c r="F9" s="13">
         <v>5600000</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Operating Expenses</v>
-      </c>
-      <c r="B5">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="13">
         <v>1800000</v>
       </c>
-      <c r="C5">
+      <c r="C10" s="13">
         <v>1950000</v>
       </c>
-      <c r="D5">
+      <c r="D10" s="13">
         <v>2150000</v>
       </c>
-      <c r="E5">
+      <c r="E10" s="13">
         <v>2400000</v>
       </c>
-      <c r="F5">
+      <c r="F10" s="13">
         <v>2600000</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>EBITDA</v>
-      </c>
-      <c r="B6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="13">
         <v>1500000</v>
       </c>
-      <c r="C6">
+      <c r="C11" s="13">
         <v>1750000</v>
       </c>
-      <c r="D6">
+      <c r="D11" s="13">
         <v>2150000</v>
       </c>
-      <c r="E6">
+      <c r="E11" s="13">
         <v>2600000</v>
       </c>
-      <c r="F6">
+      <c r="F11" s="13">
         <v>3000000</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>D&amp;A</v>
-      </c>
-      <c r="B7">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="13">
         <v>300000</v>
       </c>
-      <c r="C7">
+      <c r="C12" s="13">
         <v>330000</v>
       </c>
-      <c r="D7">
+      <c r="D12" s="13">
         <v>360000</v>
       </c>
-      <c r="E7">
+      <c r="E12" s="13">
         <v>400000</v>
       </c>
-      <c r="F7">
+      <c r="F12" s="13">
         <v>440000</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>EBIT</v>
-      </c>
-      <c r="B8">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="13">
         <v>1200000</v>
       </c>
-      <c r="C8">
+      <c r="C13" s="13">
         <v>1420000</v>
       </c>
-      <c r="D8">
+      <c r="D13" s="13">
         <v>1790000</v>
       </c>
-      <c r="E8">
+      <c r="E13" s="13">
         <v>2200000</v>
       </c>
-      <c r="F8">
+      <c r="F13" s="13">
         <v>2560000</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Interest Expense</v>
-      </c>
-      <c r="B9">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="13">
         <v>180000</v>
       </c>
-      <c r="C9">
+      <c r="C14" s="13">
         <v>170000</v>
       </c>
-      <c r="D9">
+      <c r="D14" s="13">
         <v>160000</v>
       </c>
-      <c r="E9">
+      <c r="E14" s="13">
         <v>150000</v>
       </c>
-      <c r="F9">
+      <c r="F14" s="13">
         <v>140000</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Net Income</v>
-      </c>
-      <c r="B10">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="13">
         <v>765000</v>
       </c>
-      <c r="C10">
+      <c r="C15" s="13">
         <v>937500</v>
       </c>
-      <c r="D10">
+      <c r="D15" s="13">
         <v>1222500</v>
       </c>
-      <c r="E10">
+      <c r="E15" s="13">
         <v>1537500</v>
       </c>
-      <c r="F10">
+      <c r="F15" s="13">
         <v>1815000</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="B11">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="13">
         <v>900000</v>
       </c>
-      <c r="C11">
+      <c r="C16" s="13">
         <v>1100000</v>
       </c>
-      <c r="D11">
+      <c r="D16" s="13">
         <v>1400000</v>
       </c>
-      <c r="E11">
+      <c r="E16" s="13">
         <v>1800000</v>
       </c>
-      <c r="F11">
+      <c r="F16" s="13">
         <v>2300000</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Current Assets</v>
-      </c>
-      <c r="B12">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="13">
         <v>3100000</v>
       </c>
-      <c r="C12">
+      <c r="C17" s="13">
         <v>3500000</v>
       </c>
-      <c r="D12">
+      <c r="D17" s="13">
         <v>4000000</v>
       </c>
-      <c r="E12">
+      <c r="E17" s="13">
         <v>4600000</v>
       </c>
-      <c r="F12">
+      <c r="F17" s="13">
         <v>5300000</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Total Assets</v>
-      </c>
-      <c r="B13">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="13">
         <v>9500000</v>
       </c>
-      <c r="C13">
+      <c r="C18" s="13">
         <v>10300000</v>
       </c>
-      <c r="D13">
+      <c r="D18" s="13">
         <v>11400000</v>
       </c>
-      <c r="E13">
+      <c r="E18" s="13">
         <v>12600000</v>
       </c>
-      <c r="F13">
+      <c r="F18" s="13">
         <v>14000000</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Current Liabilities</v>
-      </c>
-      <c r="B14">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="13">
         <v>1900000</v>
       </c>
-      <c r="C14">
+      <c r="C19" s="13">
         <v>2000000</v>
       </c>
-      <c r="D14">
+      <c r="D19" s="13">
         <v>2200000</v>
       </c>
-      <c r="E14">
+      <c r="E19" s="13">
         <v>2400000</v>
       </c>
-      <c r="F14">
+      <c r="F19" s="13">
         <v>2600000</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Total Liabilities</v>
-      </c>
-      <c r="B15">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="13">
         <v>5400000</v>
       </c>
-      <c r="C15">
+      <c r="C20" s="13">
         <v>5400000</v>
       </c>
-      <c r="D15">
+      <c r="D20" s="13">
         <v>5500000</v>
       </c>
-      <c r="E15">
+      <c r="E20" s="13">
         <v>5600000</v>
       </c>
-      <c r="F15">
+      <c r="F20" s="13">
         <v>5800000</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Total Debt</v>
-      </c>
-      <c r="B16">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="13">
         <v>3000000</v>
       </c>
-      <c r="C16">
+      <c r="C21" s="13">
         <v>2800000</v>
       </c>
-      <c r="D16">
+      <c r="D21" s="13">
         <v>2600000</v>
       </c>
-      <c r="E16">
+      <c r="E21" s="13">
         <v>2400000</v>
       </c>
-      <c r="F16">
+      <c r="F21" s="13">
         <v>2200000</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Equity</v>
-      </c>
-      <c r="B17">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="13">
         <v>4100000</v>
       </c>
-      <c r="C17">
+      <c r="C22" s="13">
         <v>4900000</v>
       </c>
-      <c r="D17">
+      <c r="D22" s="13">
         <v>5900000</v>
       </c>
-      <c r="E17">
+      <c r="E22" s="13">
         <v>7000000</v>
       </c>
-      <c r="F17">
+      <c r="F22" s="13">
         <v>8200000</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>CapEx</v>
-      </c>
-      <c r="B18">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="13">
         <v>450000</v>
       </c>
-      <c r="C18">
+      <c r="C23" s="13">
         <v>500000</v>
       </c>
-      <c r="D18">
+      <c r="D23" s="13">
         <v>600000</v>
       </c>
-      <c r="E18">
+      <c r="E23" s="13">
         <v>700000</v>
       </c>
-      <c r="F18">
+      <c r="F23" s="13">
         <v>800000</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Operating Cash Flow</v>
-      </c>
-      <c r="B19">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="13">
         <v>1200000</v>
       </c>
-      <c r="C19">
+      <c r="C24" s="13">
         <v>1400000</v>
       </c>
-      <c r="D19">
+      <c r="D24" s="13">
         <v>1700000</v>
       </c>
-      <c r="E19">
+      <c r="E24" s="13">
         <v>2000000</v>
       </c>
-      <c r="F19">
+      <c r="F24" s="13">
         <v>2400000</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F19"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF0B2545"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E49"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="14">
+        <v>13100000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="15">
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="15">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="15">
+        <v>0.22899999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="15">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="15">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="15">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="14">
+        <v>-100000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="16">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="17">
+        <v>21086206.73947019</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="17">
+        <v>29064220.406631395</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="17">
+        <v>38563708.625052854</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="17">
+        <v>29148440.384893242</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="18">
+        <v>0.4955</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="14">
+        <v>14862385.238789856</v>
+      </c>
+      <c r="C26" s="14">
+        <v>16223488.936634602</v>
+      </c>
+      <c r="D26" s="16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="14">
+        <v>16223488.936634602</v>
+      </c>
+      <c r="C27" s="14">
+        <v>17584592.634479348</v>
+      </c>
+      <c r="D27" s="16">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="14">
+        <v>17584592.634479348</v>
+      </c>
+      <c r="C28" s="14">
+        <v>18945696.33232409</v>
+      </c>
+      <c r="D28" s="16">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" s="14">
+        <v>18945696.33232409</v>
+      </c>
+      <c r="C29" s="14">
+        <v>20306800.030168835</v>
+      </c>
+      <c r="D29" s="16">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="14">
+        <v>20306800.030168835</v>
+      </c>
+      <c r="C30" s="14">
+        <v>21667903.728013583</v>
+      </c>
+      <c r="D30" s="16">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="14">
+        <v>21667903.728013583</v>
+      </c>
+      <c r="C31" s="14">
+        <v>23029007.425858326</v>
+      </c>
+      <c r="D31" s="16">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" s="14">
+        <v>23029007.425858326</v>
+      </c>
+      <c r="C32" s="14">
+        <v>24390111.12370307</v>
+      </c>
+      <c r="D32" s="16">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="14">
+        <v>24390111.12370307</v>
+      </c>
+      <c r="C33" s="14">
+        <v>25751214.821547814</v>
+      </c>
+      <c r="D33" s="16">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="14">
+        <v>25751214.821547814</v>
+      </c>
+      <c r="C34" s="14">
+        <v>27112318.51939256</v>
+      </c>
+      <c r="D34" s="16">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="14">
+        <v>27112318.51939256</v>
+      </c>
+      <c r="C35" s="14">
+        <v>28473422.217237305</v>
+      </c>
+      <c r="D35" s="16">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="14">
+        <v>28473422.217237305</v>
+      </c>
+      <c r="C36" s="14">
+        <v>29834525.915082052</v>
+      </c>
+      <c r="D36" s="16">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="14">
+        <v>29834525.915082052</v>
+      </c>
+      <c r="C37" s="14">
+        <v>31195629.612926796</v>
+      </c>
+      <c r="D37" s="16">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" s="14">
+        <v>31195629.612926796</v>
+      </c>
+      <c r="C38" s="14">
+        <v>32556733.31077154</v>
+      </c>
+      <c r="D38" s="16">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" s="14">
+        <v>32556733.31077154</v>
+      </c>
+      <c r="C39" s="14">
+        <v>33917837.00861628</v>
+      </c>
+      <c r="D39" s="16">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40" s="14">
+        <v>33917837.00861628</v>
+      </c>
+      <c r="C40" s="14">
+        <v>35278940.70646103</v>
+      </c>
+      <c r="D40" s="16">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B41" s="14">
+        <v>35278940.70646103</v>
+      </c>
+      <c r="C41" s="14">
+        <v>36640044.40430577</v>
+      </c>
+      <c r="D41" s="16">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B42" s="14">
+        <v>36640044.40430577</v>
+      </c>
+      <c r="C42" s="14">
+        <v>38001148.102150515</v>
+      </c>
+      <c r="D42" s="16">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" s="14">
+        <v>38001148.102150515</v>
+      </c>
+      <c r="C43" s="14">
+        <v>39362251.799995266</v>
+      </c>
+      <c r="D43" s="16">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" s="14">
+        <v>39362251.799995266</v>
+      </c>
+      <c r="C44" s="14">
+        <v>40723355.49784001</v>
+      </c>
+      <c r="D44" s="16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B45" s="14">
+        <v>40723355.49784001</v>
+      </c>
+      <c r="C45" s="14">
+        <v>42084459.19568475</v>
+      </c>
+      <c r="D45" s="16">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" s="14">
+        <v>42084459.19568475</v>
+      </c>
+      <c r="C46" s="14">
+        <v>43445562.893529505</v>
+      </c>
+      <c r="D46" s="16">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" s="14">
+        <v>43445562.893529505</v>
+      </c>
+      <c r="C47" s="14">
+        <v>44806666.59137425</v>
+      </c>
+      <c r="D47" s="16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" s="14">
+        <v>44806666.59137425</v>
+      </c>
+      <c r="C48" s="14">
+        <v>46167770.28921899</v>
+      </c>
+      <c r="D48" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B49" s="14">
+        <v>46167770.28921899</v>
+      </c>
+      <c r="C49" s="14">
+        <v>47528873.987063736</v>
+      </c>
+      <c r="D49" s="16">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>